--- a/data/trans_orig/IP09C_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP09C_R-Clase-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>57,51%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>569</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>814</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>523</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,1%</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9876</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,4%</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>606</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4134,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>138</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5470,12 +5470,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>56,66%</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6265,12 +6265,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>14254</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>12382</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6343,12 +6343,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>23987</t>
+          <t>23054</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>10385</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>25596</t>
+          <t>26195</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6534,12 +6534,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>20248</t>
+          <t>20650</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>34057</t>
+          <t>33374</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38863</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>56109</t>
+          <t>56344</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -6632,12 +6632,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6667,12 +6667,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>26435</t>
+          <t>25217</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -6745,12 +6745,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>15274</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>19694</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -6858,12 +6858,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>16574</t>
+          <t>17294</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -7548,12 +7548,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>698</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -7661,12 +7661,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>752</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7711,12 +7711,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -8569,12 +8569,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8619,12 +8619,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8654,12 +8654,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -8908,12 +8908,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>537</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8978,12 +8978,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -9143,7 +9143,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9301,12 +9301,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9321,12 +9321,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9336,12 +9336,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -9477,12 +9477,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9527,12 +9527,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9547,12 +9547,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9562,12 +9562,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>77,92%</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -10046,12 +10046,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10061,12 +10061,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10081,12 +10081,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10096,12 +10096,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15594</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -10159,12 +10159,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10229,12 +10229,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10244,12 +10244,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10322,12 +10322,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10357,12 +10357,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -10385,12 +10385,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13226</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10400,12 +10400,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10435,12 +10435,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>25275</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38762</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -10611,12 +10611,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -10626,12 +10626,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>15563</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -10724,12 +10724,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10739,12 +10739,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -10954,12 +10954,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10969,12 +10969,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -11293,12 +11293,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -11308,12 +11308,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -11411,7 +11411,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -11519,12 +11519,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>593</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -11632,12 +11632,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11647,12 +11647,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11667,12 +11667,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>750</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11682,12 +11682,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11702,12 +11702,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11717,12 +11717,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -12201,12 +12201,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>590</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12216,12 +12216,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12271,12 +12271,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12286,12 +12286,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>58,94%</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -12770,12 +12770,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12785,12 +12785,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12805,12 +12805,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12820,12 +12820,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12840,12 +12840,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>19130</t>
+          <t>19578</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>35097</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12855,12 +12855,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -12883,12 +12883,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12918,12 +12918,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12933,12 +12933,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12953,12 +12953,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12968,12 +12968,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -12996,12 +12996,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13011,12 +13011,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -13031,12 +13031,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -13046,12 +13046,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -13066,12 +13066,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -13081,12 +13081,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -13109,12 +13109,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>43315</t>
+          <t>43158</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13124,12 +13124,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -13144,12 +13144,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>29247</t>
+          <t>29632</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>45355</t>
+          <t>44654</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -13159,12 +13159,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -13179,12 +13179,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>63640</t>
+          <t>62580</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>83510</t>
+          <t>84094</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -13194,12 +13194,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -13222,12 +13222,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13237,12 +13237,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13257,12 +13257,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13292,12 +13292,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13307,12 +13307,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -13335,12 +13335,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13350,12 +13350,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -13370,12 +13370,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>13654</t>
+          <t>13674</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -13385,12 +13385,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -13405,12 +13405,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -13420,12 +13420,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -13448,12 +13448,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -13463,12 +13463,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -13483,12 +13483,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>7094</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -13498,12 +13498,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -13518,12 +13518,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>27917</t>
+          <t>27592</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -13533,12 +13533,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14143,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14223,12 +14223,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -14251,12 +14251,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>395</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -14266,12 +14266,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -14301,12 +14301,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14336,12 +14336,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14384,7 +14384,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14454,7 +14454,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>43,96%</t>
         </is>
       </c>
     </row>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14645,7 +14645,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -14855,12 +14855,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>537</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14870,12 +14870,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14905,12 +14905,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -15194,12 +15194,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>521</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -15209,12 +15209,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15244,12 +15244,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,97%</t>
         </is>
       </c>
     </row>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>46,34%</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15470,12 +15470,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>48,87%</t>
         </is>
       </c>
     </row>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15783,7 +15783,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -16029,7 +16029,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -16072,7 +16072,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -16122,7 +16122,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -16137,12 +16137,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>525</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16152,12 +16152,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16235,7 +16235,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16250,12 +16250,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16265,12 +16265,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>52,07%</t>
         </is>
       </c>
     </row>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -16411,7 +16411,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16426,7 +16426,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16481,7 +16481,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -16636,12 +16636,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16651,12 +16651,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16671,12 +16671,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16686,12 +16686,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16706,12 +16706,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16721,12 +16721,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,74%</t>
         </is>
       </c>
     </row>
@@ -16754,7 +16754,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16769,7 +16769,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16839,7 +16839,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -16867,7 +16867,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16917,7 +16917,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16932,12 +16932,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16952,7 +16952,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -16975,12 +16975,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16990,12 +16990,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -17010,12 +17010,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -17025,12 +17025,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -17045,12 +17045,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15691</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -17060,12 +17060,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -17093,7 +17093,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -17128,7 +17128,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17158,12 +17158,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>565</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17173,12 +17173,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -17201,82 +17201,82 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>4465</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>29,27%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
           <t>472</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>4459</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>29,23%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17369,7 +17369,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17559,12 +17559,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17614,12 +17614,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17629,12 +17629,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -17662,7 +17662,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17697,7 +17697,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17712,7 +17712,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17727,12 +17727,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>537</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17742,12 +17742,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -17883,12 +17883,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17898,12 +17898,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -17918,12 +17918,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17933,12 +17933,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -17953,12 +17953,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -17968,12 +17968,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -18036,7 +18036,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -18071,7 +18071,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5574</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -18109,12 +18109,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -18124,12 +18124,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -18179,12 +18179,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1391</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -18194,12 +18194,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -18262,7 +18262,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -18297,7 +18297,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -18487,12 +18487,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -18502,12 +18502,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -18522,12 +18522,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18537,12 +18537,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>72,87%</t>
         </is>
       </c>
     </row>
@@ -18831,7 +18831,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18861,12 +18861,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18876,12 +18876,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>61,99%</t>
         </is>
       </c>
     </row>
@@ -18944,7 +18944,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18959,7 +18959,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -19057,7 +19057,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -19072,7 +19072,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -19107,7 +19107,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -19360,12 +19360,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -19375,12 +19375,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -19395,12 +19395,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>16170</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -19410,12 +19410,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19430,12 +19430,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>13361</t>
+          <t>13345</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>25833</t>
+          <t>26246</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19445,12 +19445,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -19473,12 +19473,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>530</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19488,12 +19488,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19543,12 +19543,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19558,12 +19558,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -19586,12 +19586,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19601,12 +19601,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19621,12 +19621,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8726</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19636,12 +19636,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19671,12 +19671,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -19699,12 +19699,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>20909</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19714,12 +19714,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19734,12 +19734,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>18965</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19749,12 +19749,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19769,12 +19769,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>22963</t>
+          <t>23137</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>37645</t>
+          <t>37197</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19784,12 +19784,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -19812,12 +19812,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19827,12 +19827,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19847,12 +19847,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19862,12 +19862,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19882,12 +19882,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19897,12 +19897,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -19925,12 +19925,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -19940,12 +19940,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -19960,12 +19960,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -19975,12 +19975,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -19995,12 +19995,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -20010,12 +20010,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -20043,7 +20043,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -20073,12 +20073,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>870</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6499</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -20088,12 +20088,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -20108,12 +20108,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -20123,12 +20123,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
